--- a/tiflow-bfarm/develop/2.0.0-ballot.2/StructureDefinition-erp-tprescription-carbon-copy-logical.xlsx
+++ b/tiflow-bfarm/develop/2.0.0-ballot.2/StructureDefinition-erp-tprescription-carbon-copy-logical.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-12T14:54:45+00:00</t>
+    <t>2026-06-15T07:12:36+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/tiflow-bfarm/develop/2.0.0-ballot.2/StructureDefinition-erp-tprescription-carbon-copy-logical.xlsx
+++ b/tiflow-bfarm/develop/2.0.0-ballot.2/StructureDefinition-erp-tprescription-carbon-copy-logical.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-15T07:12:36+00:00</t>
+    <t>2026-06-15T07:48:09+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/tiflow-bfarm/develop/2.0.0-ballot.2/StructureDefinition-erp-tprescription-carbon-copy-logical.xlsx
+++ b/tiflow-bfarm/develop/2.0.0-ballot.2/StructureDefinition-erp-tprescription-carbon-copy-logical.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1326" uniqueCount="178">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1326" uniqueCount="180">
   <si>
     <t>Property</t>
   </si>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-15T07:48:09+00:00</t>
+    <t>2026-07-28T10:29:55+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -366,6 +366,10 @@
     <t>BackboneElement.modifierExtension</t>
   </si>
   <si>
+    <t xml:space="preserve">ele-1
+</t>
+  </si>
+  <si>
     <t>erp-tprescription-carbon-copy-logical.rxVerordnung.bezeichnung</t>
   </si>
   <si>
@@ -373,7 +377,7 @@
 </t>
   </si>
   <si>
-    <t>Bezeichnung Fertigarzneimittel/Wirkstoff ODER Rezeptur (verordnet). Je nach dem welcher Rezepttyp angewandt wurde liegt diese Angabe als Freitext oder strukturiert vor.</t>
+    <t>Bezeichnung des verordneten Arzneimittels. Ein T-Arzneimittel kann in Form aller vier Verordnungstypen (PZN-, Freitext-, Strukturierte Wirkstoff-, Strukturierte Rezeptur-Verordnung) verordnet werden.</t>
   </si>
   <si>
     <t>erp-tprescription-carbon-copy-logical.rxVerordnung.wirkstaerke</t>
@@ -386,11 +390,11 @@
     <t>Wirkstärke (verordnetes Arzneimittel)</t>
   </si>
   <si>
-    <t>erp-tprescription-carbon-copy-logical.rxVerordnung.darreichungsform</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Coding
-</t>
+    <t>erp-tprescription-carbon-copy-logical.rxVerordnung.darreichungsform[x]</t>
+  </si>
+  <si>
+    <t>string
+Coding</t>
   </si>
   <si>
     <t>Darreichungsform (verordnetes Arzneimittel)</t>
@@ -409,10 +413,14 @@
 </t>
   </si>
   <si>
-    <t>Dosierung (verordnetes Arzneimittel)</t>
+    <t>Dosierung (verordnetes Arzneimittel). Das Profil entspricht DosageDgMp des [IG DE Medication](https://ig.fhir.de/igs/medication/1.0.7/)</t>
   </si>
   <si>
     <t>erp-tprescription-carbon-copy-logical.rxVerordnung.reichdauer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Duration
+</t>
   </si>
   <si>
     <t>Reichdauer (verordnetes Arzneimittel)</t>
@@ -1720,7 +1728,7 @@
         <v>75</v>
       </c>
       <c r="AI8" t="s" s="2">
-        <v>73</v>
+        <v>113</v>
       </c>
       <c r="AJ8" t="s" s="2">
         <v>105</v>
@@ -1728,10 +1736,10 @@
     </row>
     <row r="9">
       <c r="A9" t="s" s="2">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="B9" t="s" s="2">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="C9" s="2"/>
       <c r="D9" t="s" s="2">
@@ -1754,13 +1762,13 @@
         <v>73</v>
       </c>
       <c r="K9" t="s" s="2">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="L9" t="s" s="2">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="M9" t="s" s="2">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="N9" s="2"/>
       <c r="O9" s="2"/>
@@ -1811,7 +1819,7 @@
         <v>73</v>
       </c>
       <c r="AF9" t="s" s="2">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="AG9" t="s" s="2">
         <v>74</v>
@@ -1828,10 +1836,10 @@
     </row>
     <row r="10">
       <c r="A10" t="s" s="2">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="B10" t="s" s="2">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="C10" s="2"/>
       <c r="D10" t="s" s="2">
@@ -1854,13 +1862,13 @@
         <v>73</v>
       </c>
       <c r="K10" t="s" s="2">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="L10" t="s" s="2">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="M10" t="s" s="2">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="N10" s="2"/>
       <c r="O10" s="2"/>
@@ -1911,7 +1919,7 @@
         <v>73</v>
       </c>
       <c r="AF10" t="s" s="2">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="AG10" t="s" s="2">
         <v>74</v>
@@ -1928,10 +1936,10 @@
     </row>
     <row r="11">
       <c r="A11" t="s" s="2">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="B11" t="s" s="2">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="C11" s="2"/>
       <c r="D11" t="s" s="2">
@@ -1954,13 +1962,13 @@
         <v>73</v>
       </c>
       <c r="K11" t="s" s="2">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="L11" t="s" s="2">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="M11" t="s" s="2">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="N11" s="2"/>
       <c r="O11" s="2"/>
@@ -2011,7 +2019,7 @@
         <v>73</v>
       </c>
       <c r="AF11" t="s" s="2">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="AG11" t="s" s="2">
         <v>74</v>
@@ -2028,10 +2036,10 @@
     </row>
     <row r="12">
       <c r="A12" t="s" s="2">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="B12" t="s" s="2">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="C12" s="2"/>
       <c r="D12" t="s" s="2">
@@ -2054,13 +2062,13 @@
         <v>73</v>
       </c>
       <c r="K12" t="s" s="2">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="L12" t="s" s="2">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="M12" t="s" s="2">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="N12" s="2"/>
       <c r="O12" s="2"/>
@@ -2111,7 +2119,7 @@
         <v>73</v>
       </c>
       <c r="AF12" t="s" s="2">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="AG12" t="s" s="2">
         <v>74</v>
@@ -2128,10 +2136,10 @@
     </row>
     <row r="13">
       <c r="A13" t="s" s="2">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="B13" t="s" s="2">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="C13" s="2"/>
       <c r="D13" t="s" s="2">
@@ -2154,13 +2162,13 @@
         <v>73</v>
       </c>
       <c r="K13" t="s" s="2">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="L13" t="s" s="2">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="M13" t="s" s="2">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="N13" s="2"/>
       <c r="O13" s="2"/>
@@ -2211,7 +2219,7 @@
         <v>73</v>
       </c>
       <c r="AF13" t="s" s="2">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="AG13" t="s" s="2">
         <v>74</v>
@@ -2228,10 +2236,10 @@
     </row>
     <row r="14">
       <c r="A14" t="s" s="2">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="B14" t="s" s="2">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="C14" s="2"/>
       <c r="D14" t="s" s="2">
@@ -2254,13 +2262,13 @@
         <v>73</v>
       </c>
       <c r="K14" t="s" s="2">
-        <v>91</v>
+        <v>129</v>
       </c>
       <c r="L14" t="s" s="2">
-        <v>128</v>
+        <v>130</v>
       </c>
       <c r="M14" t="s" s="2">
-        <v>128</v>
+        <v>130</v>
       </c>
       <c r="N14" s="2"/>
       <c r="O14" s="2"/>
@@ -2311,7 +2319,7 @@
         <v>73</v>
       </c>
       <c r="AF14" t="s" s="2">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="AG14" t="s" s="2">
         <v>79</v>
@@ -2328,10 +2336,10 @@
     </row>
     <row r="15">
       <c r="A15" t="s" s="2">
-        <v>129</v>
+        <v>131</v>
       </c>
       <c r="B15" t="s" s="2">
-        <v>129</v>
+        <v>131</v>
       </c>
       <c r="C15" s="2"/>
       <c r="D15" t="s" s="2">
@@ -2357,10 +2365,10 @@
         <v>87</v>
       </c>
       <c r="L15" t="s" s="2">
-        <v>130</v>
+        <v>132</v>
       </c>
       <c r="M15" t="s" s="2">
-        <v>130</v>
+        <v>132</v>
       </c>
       <c r="N15" s="2"/>
       <c r="O15" s="2"/>
@@ -2411,7 +2419,7 @@
         <v>73</v>
       </c>
       <c r="AF15" t="s" s="2">
-        <v>129</v>
+        <v>131</v>
       </c>
       <c r="AG15" t="s" s="2">
         <v>79</v>
@@ -2428,10 +2436,10 @@
     </row>
     <row r="16">
       <c r="A16" t="s" s="2">
-        <v>131</v>
+        <v>133</v>
       </c>
       <c r="B16" t="s" s="2">
-        <v>131</v>
+        <v>133</v>
       </c>
       <c r="C16" s="2"/>
       <c r="D16" t="s" s="2">
@@ -2528,10 +2536,10 @@
     </row>
     <row r="17">
       <c r="A17" t="s" s="2">
-        <v>132</v>
+        <v>134</v>
       </c>
       <c r="B17" t="s" s="2">
-        <v>132</v>
+        <v>134</v>
       </c>
       <c r="C17" s="2"/>
       <c r="D17" t="s" s="2">
@@ -2630,10 +2638,10 @@
     </row>
     <row r="18">
       <c r="A18" t="s" s="2">
-        <v>133</v>
+        <v>135</v>
       </c>
       <c r="B18" t="s" s="2">
-        <v>133</v>
+        <v>135</v>
       </c>
       <c r="C18" s="2"/>
       <c r="D18" t="s" s="2">
@@ -2726,7 +2734,7 @@
         <v>75</v>
       </c>
       <c r="AI18" t="s" s="2">
-        <v>73</v>
+        <v>113</v>
       </c>
       <c r="AJ18" t="s" s="2">
         <v>105</v>
@@ -2734,10 +2742,10 @@
     </row>
     <row r="19">
       <c r="A19" t="s" s="2">
-        <v>134</v>
+        <v>136</v>
       </c>
       <c r="B19" t="s" s="2">
-        <v>134</v>
+        <v>136</v>
       </c>
       <c r="C19" s="2"/>
       <c r="D19" t="s" s="2">
@@ -2760,13 +2768,13 @@
         <v>73</v>
       </c>
       <c r="K19" t="s" s="2">
-        <v>135</v>
+        <v>137</v>
       </c>
       <c r="L19" t="s" s="2">
-        <v>136</v>
+        <v>138</v>
       </c>
       <c r="M19" t="s" s="2">
-        <v>136</v>
+        <v>138</v>
       </c>
       <c r="N19" s="2"/>
       <c r="O19" s="2"/>
@@ -2817,7 +2825,7 @@
         <v>73</v>
       </c>
       <c r="AF19" t="s" s="2">
-        <v>134</v>
+        <v>136</v>
       </c>
       <c r="AG19" t="s" s="2">
         <v>79</v>
@@ -2834,10 +2842,10 @@
     </row>
     <row r="20">
       <c r="A20" t="s" s="2">
-        <v>137</v>
+        <v>139</v>
       </c>
       <c r="B20" t="s" s="2">
-        <v>137</v>
+        <v>139</v>
       </c>
       <c r="C20" s="2"/>
       <c r="D20" t="s" s="2">
@@ -2860,13 +2868,13 @@
         <v>73</v>
       </c>
       <c r="K20" t="s" s="2">
-        <v>135</v>
+        <v>137</v>
       </c>
       <c r="L20" t="s" s="2">
-        <v>138</v>
+        <v>140</v>
       </c>
       <c r="M20" t="s" s="2">
-        <v>138</v>
+        <v>140</v>
       </c>
       <c r="N20" s="2"/>
       <c r="O20" s="2"/>
@@ -2917,7 +2925,7 @@
         <v>73</v>
       </c>
       <c r="AF20" t="s" s="2">
-        <v>137</v>
+        <v>139</v>
       </c>
       <c r="AG20" t="s" s="2">
         <v>79</v>
@@ -2934,10 +2942,10 @@
     </row>
     <row r="21">
       <c r="A21" t="s" s="2">
-        <v>139</v>
+        <v>141</v>
       </c>
       <c r="B21" t="s" s="2">
-        <v>139</v>
+        <v>141</v>
       </c>
       <c r="C21" s="2"/>
       <c r="D21" t="s" s="2">
@@ -2960,13 +2968,13 @@
         <v>73</v>
       </c>
       <c r="K21" t="s" s="2">
-        <v>135</v>
+        <v>137</v>
       </c>
       <c r="L21" t="s" s="2">
-        <v>140</v>
+        <v>142</v>
       </c>
       <c r="M21" t="s" s="2">
-        <v>140</v>
+        <v>142</v>
       </c>
       <c r="N21" s="2"/>
       <c r="O21" s="2"/>
@@ -3017,7 +3025,7 @@
         <v>73</v>
       </c>
       <c r="AF21" t="s" s="2">
-        <v>139</v>
+        <v>141</v>
       </c>
       <c r="AG21" t="s" s="2">
         <v>79</v>
@@ -3034,10 +3042,10 @@
     </row>
     <row r="22">
       <c r="A22" t="s" s="2">
-        <v>141</v>
+        <v>143</v>
       </c>
       <c r="B22" t="s" s="2">
-        <v>141</v>
+        <v>143</v>
       </c>
       <c r="C22" s="2"/>
       <c r="D22" t="s" s="2">
@@ -3060,13 +3068,13 @@
         <v>73</v>
       </c>
       <c r="K22" t="s" s="2">
-        <v>135</v>
+        <v>137</v>
       </c>
       <c r="L22" t="s" s="2">
-        <v>142</v>
+        <v>144</v>
       </c>
       <c r="M22" t="s" s="2">
-        <v>142</v>
+        <v>144</v>
       </c>
       <c r="N22" s="2"/>
       <c r="O22" s="2"/>
@@ -3117,7 +3125,7 @@
         <v>73</v>
       </c>
       <c r="AF22" t="s" s="2">
-        <v>141</v>
+        <v>143</v>
       </c>
       <c r="AG22" t="s" s="2">
         <v>79</v>
@@ -3134,10 +3142,10 @@
     </row>
     <row r="23">
       <c r="A23" t="s" s="2">
-        <v>143</v>
+        <v>145</v>
       </c>
       <c r="B23" t="s" s="2">
-        <v>143</v>
+        <v>145</v>
       </c>
       <c r="C23" s="2"/>
       <c r="D23" t="s" s="2">
@@ -3160,13 +3168,13 @@
         <v>73</v>
       </c>
       <c r="K23" t="s" s="2">
-        <v>135</v>
+        <v>137</v>
       </c>
       <c r="L23" t="s" s="2">
-        <v>144</v>
+        <v>146</v>
       </c>
       <c r="M23" t="s" s="2">
-        <v>144</v>
+        <v>146</v>
       </c>
       <c r="N23" s="2"/>
       <c r="O23" s="2"/>
@@ -3217,7 +3225,7 @@
         <v>73</v>
       </c>
       <c r="AF23" t="s" s="2">
-        <v>143</v>
+        <v>145</v>
       </c>
       <c r="AG23" t="s" s="2">
         <v>79</v>
@@ -3234,10 +3242,10 @@
     </row>
     <row r="24">
       <c r="A24" t="s" s="2">
-        <v>145</v>
+        <v>147</v>
       </c>
       <c r="B24" t="s" s="2">
-        <v>145</v>
+        <v>147</v>
       </c>
       <c r="C24" s="2"/>
       <c r="D24" t="s" s="2">
@@ -3263,10 +3271,10 @@
         <v>87</v>
       </c>
       <c r="L24" t="s" s="2">
-        <v>146</v>
+        <v>148</v>
       </c>
       <c r="M24" t="s" s="2">
-        <v>146</v>
+        <v>148</v>
       </c>
       <c r="N24" s="2"/>
       <c r="O24" s="2"/>
@@ -3317,7 +3325,7 @@
         <v>73</v>
       </c>
       <c r="AF24" t="s" s="2">
-        <v>145</v>
+        <v>147</v>
       </c>
       <c r="AG24" t="s" s="2">
         <v>79</v>
@@ -3334,10 +3342,10 @@
     </row>
     <row r="25">
       <c r="A25" t="s" s="2">
-        <v>147</v>
+        <v>149</v>
       </c>
       <c r="B25" t="s" s="2">
-        <v>147</v>
+        <v>149</v>
       </c>
       <c r="C25" s="2"/>
       <c r="D25" t="s" s="2">
@@ -3434,10 +3442,10 @@
     </row>
     <row r="26">
       <c r="A26" t="s" s="2">
-        <v>148</v>
+        <v>150</v>
       </c>
       <c r="B26" t="s" s="2">
-        <v>148</v>
+        <v>150</v>
       </c>
       <c r="C26" s="2"/>
       <c r="D26" t="s" s="2">
@@ -3536,10 +3544,10 @@
     </row>
     <row r="27">
       <c r="A27" t="s" s="2">
-        <v>149</v>
+        <v>151</v>
       </c>
       <c r="B27" t="s" s="2">
-        <v>149</v>
+        <v>151</v>
       </c>
       <c r="C27" s="2"/>
       <c r="D27" t="s" s="2">
@@ -3632,7 +3640,7 @@
         <v>75</v>
       </c>
       <c r="AI27" t="s" s="2">
-        <v>73</v>
+        <v>113</v>
       </c>
       <c r="AJ27" t="s" s="2">
         <v>105</v>
@@ -3640,10 +3648,10 @@
     </row>
     <row r="28">
       <c r="A28" t="s" s="2">
-        <v>150</v>
+        <v>152</v>
       </c>
       <c r="B28" t="s" s="2">
-        <v>150</v>
+        <v>152</v>
       </c>
       <c r="C28" s="2"/>
       <c r="D28" t="s" s="2">
@@ -3666,13 +3674,13 @@
         <v>73</v>
       </c>
       <c r="K28" t="s" s="2">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="L28" t="s" s="2">
-        <v>151</v>
+        <v>153</v>
       </c>
       <c r="M28" t="s" s="2">
-        <v>151</v>
+        <v>153</v>
       </c>
       <c r="N28" s="2"/>
       <c r="O28" s="2"/>
@@ -3723,7 +3731,7 @@
         <v>73</v>
       </c>
       <c r="AF28" t="s" s="2">
-        <v>150</v>
+        <v>152</v>
       </c>
       <c r="AG28" t="s" s="2">
         <v>79</v>
@@ -3740,10 +3748,10 @@
     </row>
     <row r="29">
       <c r="A29" t="s" s="2">
-        <v>152</v>
+        <v>154</v>
       </c>
       <c r="B29" t="s" s="2">
-        <v>152</v>
+        <v>154</v>
       </c>
       <c r="C29" s="2"/>
       <c r="D29" t="s" s="2">
@@ -3766,13 +3774,13 @@
         <v>73</v>
       </c>
       <c r="K29" t="s" s="2">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="L29" t="s" s="2">
-        <v>153</v>
+        <v>155</v>
       </c>
       <c r="M29" t="s" s="2">
-        <v>153</v>
+        <v>155</v>
       </c>
       <c r="N29" s="2"/>
       <c r="O29" s="2"/>
@@ -3823,7 +3831,7 @@
         <v>73</v>
       </c>
       <c r="AF29" t="s" s="2">
-        <v>152</v>
+        <v>154</v>
       </c>
       <c r="AG29" t="s" s="2">
         <v>74</v>
@@ -3840,10 +3848,10 @@
     </row>
     <row r="30">
       <c r="A30" t="s" s="2">
-        <v>154</v>
+        <v>156</v>
       </c>
       <c r="B30" t="s" s="2">
-        <v>154</v>
+        <v>156</v>
       </c>
       <c r="C30" s="2"/>
       <c r="D30" t="s" s="2">
@@ -3869,10 +3877,10 @@
         <v>91</v>
       </c>
       <c r="L30" t="s" s="2">
-        <v>155</v>
+        <v>157</v>
       </c>
       <c r="M30" t="s" s="2">
-        <v>155</v>
+        <v>157</v>
       </c>
       <c r="N30" s="2"/>
       <c r="O30" s="2"/>
@@ -3923,7 +3931,7 @@
         <v>73</v>
       </c>
       <c r="AF30" t="s" s="2">
-        <v>154</v>
+        <v>156</v>
       </c>
       <c r="AG30" t="s" s="2">
         <v>74</v>
@@ -3940,10 +3948,10 @@
     </row>
     <row r="31">
       <c r="A31" t="s" s="2">
-        <v>156</v>
+        <v>158</v>
       </c>
       <c r="B31" t="s" s="2">
-        <v>156</v>
+        <v>158</v>
       </c>
       <c r="C31" s="2"/>
       <c r="D31" t="s" s="2">
@@ -3966,13 +3974,13 @@
         <v>73</v>
       </c>
       <c r="K31" t="s" s="2">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="L31" t="s" s="2">
-        <v>157</v>
+        <v>159</v>
       </c>
       <c r="M31" t="s" s="2">
-        <v>157</v>
+        <v>159</v>
       </c>
       <c r="N31" s="2"/>
       <c r="O31" s="2"/>
@@ -4023,7 +4031,7 @@
         <v>73</v>
       </c>
       <c r="AF31" t="s" s="2">
-        <v>156</v>
+        <v>158</v>
       </c>
       <c r="AG31" t="s" s="2">
         <v>74</v>
@@ -4040,10 +4048,10 @@
     </row>
     <row r="32">
       <c r="A32" t="s" s="2">
-        <v>158</v>
+        <v>160</v>
       </c>
       <c r="B32" t="s" s="2">
-        <v>158</v>
+        <v>160</v>
       </c>
       <c r="C32" s="2"/>
       <c r="D32" t="s" s="2">
@@ -4066,13 +4074,13 @@
         <v>73</v>
       </c>
       <c r="K32" t="s" s="2">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="L32" t="s" s="2">
-        <v>159</v>
+        <v>161</v>
       </c>
       <c r="M32" t="s" s="2">
-        <v>159</v>
+        <v>161</v>
       </c>
       <c r="N32" s="2"/>
       <c r="O32" s="2"/>
@@ -4123,7 +4131,7 @@
         <v>73</v>
       </c>
       <c r="AF32" t="s" s="2">
-        <v>158</v>
+        <v>160</v>
       </c>
       <c r="AG32" t="s" s="2">
         <v>74</v>
@@ -4140,10 +4148,10 @@
     </row>
     <row r="33">
       <c r="A33" t="s" s="2">
-        <v>160</v>
+        <v>162</v>
       </c>
       <c r="B33" t="s" s="2">
-        <v>160</v>
+        <v>162</v>
       </c>
       <c r="C33" s="2"/>
       <c r="D33" t="s" s="2">
@@ -4166,13 +4174,13 @@
         <v>73</v>
       </c>
       <c r="K33" t="s" s="2">
-        <v>161</v>
+        <v>163</v>
       </c>
       <c r="L33" t="s" s="2">
-        <v>162</v>
+        <v>164</v>
       </c>
       <c r="M33" t="s" s="2">
-        <v>162</v>
+        <v>164</v>
       </c>
       <c r="N33" s="2"/>
       <c r="O33" s="2"/>
@@ -4223,7 +4231,7 @@
         <v>73</v>
       </c>
       <c r="AF33" t="s" s="2">
-        <v>160</v>
+        <v>162</v>
       </c>
       <c r="AG33" t="s" s="2">
         <v>79</v>
@@ -4240,10 +4248,10 @@
     </row>
     <row r="34">
       <c r="A34" t="s" s="2">
-        <v>163</v>
+        <v>165</v>
       </c>
       <c r="B34" t="s" s="2">
-        <v>163</v>
+        <v>165</v>
       </c>
       <c r="C34" s="2"/>
       <c r="D34" t="s" s="2">
@@ -4269,10 +4277,10 @@
         <v>87</v>
       </c>
       <c r="L34" t="s" s="2">
-        <v>164</v>
+        <v>166</v>
       </c>
       <c r="M34" t="s" s="2">
-        <v>164</v>
+        <v>166</v>
       </c>
       <c r="N34" s="2"/>
       <c r="O34" s="2"/>
@@ -4323,7 +4331,7 @@
         <v>73</v>
       </c>
       <c r="AF34" t="s" s="2">
-        <v>163</v>
+        <v>165</v>
       </c>
       <c r="AG34" t="s" s="2">
         <v>79</v>
@@ -4340,10 +4348,10 @@
     </row>
     <row r="35">
       <c r="A35" t="s" s="2">
-        <v>165</v>
+        <v>167</v>
       </c>
       <c r="B35" t="s" s="2">
-        <v>165</v>
+        <v>167</v>
       </c>
       <c r="C35" s="2"/>
       <c r="D35" t="s" s="2">
@@ -4440,10 +4448,10 @@
     </row>
     <row r="36">
       <c r="A36" t="s" s="2">
-        <v>166</v>
+        <v>168</v>
       </c>
       <c r="B36" t="s" s="2">
-        <v>166</v>
+        <v>168</v>
       </c>
       <c r="C36" s="2"/>
       <c r="D36" t="s" s="2">
@@ -4542,10 +4550,10 @@
     </row>
     <row r="37">
       <c r="A37" t="s" s="2">
-        <v>167</v>
+        <v>169</v>
       </c>
       <c r="B37" t="s" s="2">
-        <v>167</v>
+        <v>169</v>
       </c>
       <c r="C37" s="2"/>
       <c r="D37" t="s" s="2">
@@ -4638,7 +4646,7 @@
         <v>75</v>
       </c>
       <c r="AI37" t="s" s="2">
-        <v>73</v>
+        <v>113</v>
       </c>
       <c r="AJ37" t="s" s="2">
         <v>105</v>
@@ -4646,10 +4654,10 @@
     </row>
     <row r="38">
       <c r="A38" t="s" s="2">
-        <v>168</v>
+        <v>170</v>
       </c>
       <c r="B38" t="s" s="2">
-        <v>168</v>
+        <v>170</v>
       </c>
       <c r="C38" s="2"/>
       <c r="D38" t="s" s="2">
@@ -4675,10 +4683,10 @@
         <v>91</v>
       </c>
       <c r="L38" t="s" s="2">
-        <v>169</v>
+        <v>171</v>
       </c>
       <c r="M38" t="s" s="2">
-        <v>169</v>
+        <v>171</v>
       </c>
       <c r="N38" s="2"/>
       <c r="O38" s="2"/>
@@ -4729,7 +4737,7 @@
         <v>73</v>
       </c>
       <c r="AF38" t="s" s="2">
-        <v>168</v>
+        <v>170</v>
       </c>
       <c r="AG38" t="s" s="2">
         <v>79</v>
@@ -4746,10 +4754,10 @@
     </row>
     <row r="39">
       <c r="A39" t="s" s="2">
-        <v>170</v>
+        <v>172</v>
       </c>
       <c r="B39" t="s" s="2">
-        <v>170</v>
+        <v>172</v>
       </c>
       <c r="C39" s="2"/>
       <c r="D39" t="s" s="2">
@@ -4775,10 +4783,10 @@
         <v>91</v>
       </c>
       <c r="L39" t="s" s="2">
-        <v>171</v>
+        <v>173</v>
       </c>
       <c r="M39" t="s" s="2">
-        <v>171</v>
+        <v>173</v>
       </c>
       <c r="N39" s="2"/>
       <c r="O39" s="2"/>
@@ -4829,7 +4837,7 @@
         <v>73</v>
       </c>
       <c r="AF39" t="s" s="2">
-        <v>170</v>
+        <v>172</v>
       </c>
       <c r="AG39" t="s" s="2">
         <v>74</v>
@@ -4846,10 +4854,10 @@
     </row>
     <row r="40">
       <c r="A40" t="s" s="2">
-        <v>172</v>
+        <v>174</v>
       </c>
       <c r="B40" t="s" s="2">
-        <v>172</v>
+        <v>174</v>
       </c>
       <c r="C40" s="2"/>
       <c r="D40" t="s" s="2">
@@ -4872,13 +4880,13 @@
         <v>73</v>
       </c>
       <c r="K40" t="s" s="2">
-        <v>173</v>
+        <v>175</v>
       </c>
       <c r="L40" t="s" s="2">
-        <v>174</v>
+        <v>176</v>
       </c>
       <c r="M40" t="s" s="2">
-        <v>174</v>
+        <v>176</v>
       </c>
       <c r="N40" s="2"/>
       <c r="O40" s="2"/>
@@ -4929,7 +4937,7 @@
         <v>73</v>
       </c>
       <c r="AF40" t="s" s="2">
-        <v>172</v>
+        <v>174</v>
       </c>
       <c r="AG40" t="s" s="2">
         <v>74</v>
@@ -4946,10 +4954,10 @@
     </row>
     <row r="41">
       <c r="A41" t="s" s="2">
-        <v>175</v>
+        <v>177</v>
       </c>
       <c r="B41" t="s" s="2">
-        <v>175</v>
+        <v>177</v>
       </c>
       <c r="C41" s="2"/>
       <c r="D41" t="s" s="2">
@@ -4972,13 +4980,13 @@
         <v>73</v>
       </c>
       <c r="K41" t="s" s="2">
-        <v>176</v>
+        <v>178</v>
       </c>
       <c r="L41" t="s" s="2">
-        <v>177</v>
+        <v>179</v>
       </c>
       <c r="M41" t="s" s="2">
-        <v>177</v>
+        <v>179</v>
       </c>
       <c r="N41" s="2"/>
       <c r="O41" s="2"/>
@@ -5029,7 +5037,7 @@
         <v>73</v>
       </c>
       <c r="AF41" t="s" s="2">
-        <v>175</v>
+        <v>177</v>
       </c>
       <c r="AG41" t="s" s="2">
         <v>74</v>
